--- a/StingTools/Docs/_template_sources/deliverable_tabular.xlsx
+++ b/StingTools/Docs/_template_sources/deliverable_tabular.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +25,46 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +72,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="007F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="007F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="007F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="007F7F7F"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,99 +468,245 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Planscape Limited — Tabular Deliverable</t>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>{{project.company_name}} — Tabular Deliverable Schedule</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Project:</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Document</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>{{doc.number}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>{{doc.title}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Revision</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>{{doc.revision}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Suitability</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>{{doc.suitability}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Project</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>{{project.name}}</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Document:</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>{{doc.number}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Issued</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{{doc.generated_at}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>UoM</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>{{#line_items}}</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>{{seq}}</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>{{description}}</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>{{qty}}</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>{{uom}}</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>{{material}}</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>{{remarks}}</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>{{category}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>{{/line_items}}</t>
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Total items</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>{{loops.line_items.count}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Issued by</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>{{people.issued_by}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Reviewed by</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>{{people.reviewed_by}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Approved by</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>{{people.approved_by}}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <mergeCells count="7">
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B8:G8"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="B6:G6"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9"/>
 </worksheet>
 </file>